--- a/deploy_data/cirurgias.xlsx
+++ b/deploy_data/cirurgias.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BH2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,174 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>05/03/2025</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jonas Galatti Carbonera</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ribeirão Preto</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Dr. Daniel</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Aline, Natália, Ana, thamara (extra)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3705</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3705</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>55</v>
-      </c>
-      <c r="V3" t="n">
-        <v>750</v>
-      </c>
-      <c r="W3" t="n">
-        <v>730</v>
-      </c>
-      <c r="X3" t="n">
-        <v>76</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1250</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1202</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>76</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1200</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1186</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>630</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>587</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>thamara</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>{"tipo":"Não","seringas":"","comentarios":""}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
